--- a/Graduation Project/Project Data/original/Manufacturing Downtime/Manufacturing_Line_Productivity.xlsx
+++ b/Graduation Project/Project Data/original/Manufacturing Downtime/Manufacturing_Line_Productivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abayoumi/Downloads/Manufacturing+Downtime/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ATG\Documents\GitHub\Project-DEPI\Graduation Project\Project Data\original\Manufacturing Downtime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F90452-8069-234F-B407-6E7180222928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBE059B-5348-4118-97AB-454C071916F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="140" windowWidth="12560" windowHeight="15700" xr2:uid="{8FF62ED8-A67E-423F-8325-F23DB684777C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FF62ED8-A67E-423F-8325-F23DB684777C}"/>
   </bookViews>
   <sheets>
     <sheet name="Line productivity" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -195,15 +195,50 @@
   </si>
   <si>
     <t>Root Berry</t>
+  </si>
+  <si>
+    <t>Jake</t>
+  </si>
+  <si>
+    <t>kyle</t>
+  </si>
+  <si>
+    <t>joe</t>
+  </si>
+  <si>
+    <t>George</t>
+  </si>
+  <si>
+    <t>Damian</t>
+  </si>
+  <si>
+    <t>jacop</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Harry</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>Reece</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -258,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -597,19 +632,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D962F3-8C54-4C2B-8E48-722D67F8C002}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="8.83203125" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" customWidth="1"/>
+    <col min="4" max="5" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.81640625" customWidth="1"/>
+    <col min="13" max="13" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -629,7 +664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45533</v>
       </c>
@@ -650,7 +685,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45533</v>
       </c>
@@ -661,7 +696,7 @@
         <v>422112</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3">
         <v>0.58680555555555558</v>
@@ -671,7 +706,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45533</v>
       </c>
@@ -682,7 +717,7 @@
         <v>422113</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3">
         <v>0.65625</v>
@@ -692,7 +727,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45533</v>
       </c>
@@ -703,7 +738,7 @@
         <v>422114</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3">
         <v>0.73263888888888884</v>
@@ -713,7 +748,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45533</v>
       </c>
@@ -724,7 +759,7 @@
         <v>422115</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3">
         <v>0.80208333333333326</v>
@@ -734,7 +769,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45533</v>
       </c>
@@ -745,7 +780,7 @@
         <v>422116</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3">
         <v>0.86041666666666661</v>
@@ -755,7 +790,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45533</v>
       </c>
@@ -766,7 +801,7 @@
         <v>422117</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3">
         <v>0.90208333333333324</v>
@@ -776,7 +811,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45534</v>
       </c>
@@ -787,7 +822,7 @@
         <v>422118</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3">
         <v>0.1701388888888889</v>
@@ -797,7 +832,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45534</v>
       </c>
@@ -808,7 +843,7 @@
         <v>422119</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3">
         <v>0.25347222222222221</v>
@@ -817,7 +852,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45534</v>
       </c>
@@ -828,7 +863,7 @@
         <v>422120</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3">
         <v>0.3125</v>
@@ -837,7 +872,7 @@
         <v>0.39027777777777778</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45534</v>
       </c>
@@ -848,7 +883,7 @@
         <v>422121</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3">
         <v>0.39027777777777778</v>
@@ -857,7 +892,7 @@
         <v>0.44236111111111109</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45534</v>
       </c>
@@ -868,7 +903,7 @@
         <v>422122</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3">
         <v>0.44236111111111109</v>
@@ -877,7 +912,7 @@
         <v>0.50138888888888888</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45534</v>
       </c>
@@ -888,7 +923,7 @@
         <v>422123</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3">
         <v>0.50138888888888888</v>
@@ -897,7 +932,7 @@
         <v>0.59375</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45534</v>
       </c>
@@ -908,7 +943,7 @@
         <v>422124</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3">
         <v>0.59375</v>
@@ -917,7 +952,7 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45534</v>
       </c>
@@ -928,7 +963,7 @@
         <v>422125</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3">
         <v>0.66319444444444442</v>
@@ -937,7 +972,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45534</v>
       </c>
@@ -948,7 +983,7 @@
         <v>422126</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3">
         <v>0.71875</v>
@@ -957,7 +992,7 @@
         <v>0.79097222222222219</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45534</v>
       </c>
@@ -968,7 +1003,7 @@
         <v>422127</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3">
         <v>0.79097222222222219</v>
@@ -977,7 +1012,7 @@
         <v>0.84861111111111109</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45534</v>
       </c>
@@ -997,7 +1032,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45534</v>
       </c>
@@ -1008,7 +1043,7 @@
         <v>422129</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="3">
         <v>0.92638888888888893</v>
@@ -1017,7 +1052,7 @@
         <v>0.97847222222222219</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45535</v>
       </c>
@@ -1028,7 +1063,7 @@
         <v>422130</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E21" s="3">
         <v>0.32291666666666669</v>
@@ -1037,7 +1072,7 @@
         <v>0.37847222222222221</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45535</v>
       </c>
@@ -1048,7 +1083,7 @@
         <v>422131</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3">
         <v>0.37847222222222221</v>
@@ -1057,7 +1092,7 @@
         <v>0.44097222222222221</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45535</v>
       </c>
@@ -1068,7 +1103,7 @@
         <v>422132</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E23" s="3">
         <v>0.44097222222222221</v>
@@ -1077,7 +1112,7 @@
         <v>0.4826388888888889</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45535</v>
       </c>
@@ -1088,7 +1123,7 @@
         <v>422133</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E24" s="3">
         <v>0.4826388888888889</v>
@@ -1097,7 +1132,7 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45535</v>
       </c>
@@ -1108,7 +1143,7 @@
         <v>422134</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" s="3">
         <v>0.53819444444444442</v>
@@ -1117,7 +1152,7 @@
         <v>0.61458333333333337</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45535</v>
       </c>
@@ -1128,7 +1163,7 @@
         <v>422135</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E26" s="3">
         <v>0.61458333333333337</v>
@@ -1137,7 +1172,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45535</v>
       </c>
@@ -1148,7 +1183,7 @@
         <v>422136</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3">
         <v>0.6875</v>
@@ -1157,7 +1192,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45537</v>
       </c>
@@ -1168,7 +1203,7 @@
         <v>422137</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3">
         <v>4.1666666666666664E-2</v>
@@ -1177,7 +1212,7 @@
         <v>0.11458333333333333</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45537</v>
       </c>
@@ -1188,7 +1223,7 @@
         <v>422138</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E29" s="3">
         <v>0.11458333333333333</v>
@@ -1197,7 +1232,7 @@
         <v>0.1701388888888889</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45537</v>
       </c>
@@ -1208,7 +1243,7 @@
         <v>422139</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E30" s="3">
         <v>0.1701388888888889</v>
@@ -1217,7 +1252,7 @@
         <v>0.2361111111111111</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45537</v>
       </c>
@@ -1228,7 +1263,7 @@
         <v>422140</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E31" s="3">
         <v>0.2361111111111111</v>
@@ -1237,7 +1272,7 @@
         <v>0.3215277777777778</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45537</v>
       </c>
@@ -1248,7 +1283,7 @@
         <v>422141</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E32" s="3">
         <v>0.3215277777777778</v>
@@ -1257,7 +1292,7 @@
         <v>0.36805555555555558</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45537</v>
       </c>
@@ -1268,7 +1303,7 @@
         <v>422142</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E33" s="3">
         <v>0.36805555555555558</v>
@@ -1277,7 +1312,7 @@
         <v>0.43055555555555558</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45537</v>
       </c>
@@ -1288,7 +1323,7 @@
         <v>422143</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E34" s="3">
         <v>0.43055555555555558</v>
@@ -1297,7 +1332,7 @@
         <v>0.51249999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45537</v>
       </c>
@@ -1308,7 +1343,7 @@
         <v>422144</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E35" s="3">
         <v>0.51249999999999996</v>
@@ -1317,7 +1352,7 @@
         <v>0.61805555555555558</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45537</v>
       </c>
@@ -1328,7 +1363,7 @@
         <v>422145</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36" s="3">
         <v>0.61805555555555558</v>
@@ -1337,7 +1372,7 @@
         <v>0.70138888888888895</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45537</v>
       </c>
@@ -1348,7 +1383,7 @@
         <v>422146</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="3">
         <v>0.70138888888888895</v>
@@ -1357,7 +1392,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>45537</v>
       </c>
@@ -1368,7 +1403,7 @@
         <v>422147</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E38" s="3">
         <v>0.8125</v>
@@ -1377,7 +1412,7 @@
         <v>0.95486111111111116</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>45538</v>
       </c>
@@ -1388,7 +1423,7 @@
         <v>422148</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E39" s="3">
         <v>0.95486111111111116</v>
@@ -1405,13 +1440,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FA7A9A-369F-46C5-93C5-09FBB32FF7C0}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1425,7 +1460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1439,7 +1474,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1453,7 +1488,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1467,7 +1502,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1481,7 +1516,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1495,7 +1530,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1518,14 +1553,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB7156D-DBB5-4EA9-A733-8897AD1035D5}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1536,7 +1571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1547,7 +1582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1558,7 +1593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1569,7 +1604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1580,7 +1615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1591,7 +1626,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1602,7 +1637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1613,7 +1648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1624,7 +1659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1635,7 +1670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1646,7 +1681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1657,7 +1692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1676,13 +1711,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E903E6B-C648-491E-9E5D-F67501FDD632}">
   <dimension ref="A1:M40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="13" width="5.5" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="13" width="5.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B1" s="4" t="s">
         <v>23</v>
       </c>
@@ -1698,7 +1733,7 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1739,7 +1774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>422111</v>
       </c>
@@ -1750,7 +1785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>422112</v>
       </c>
@@ -1761,7 +1796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>422113</v>
       </c>
@@ -1769,7 +1804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>422114</v>
       </c>
@@ -1780,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>422115</v>
       </c>
@@ -1788,12 +1823,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>422116</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>422117</v>
       </c>
@@ -1804,7 +1839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>422118</v>
       </c>
@@ -1821,7 +1856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>422119</v>
       </c>
@@ -1829,7 +1864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>422120</v>
       </c>
@@ -1843,7 +1878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>422121</v>
       </c>
@@ -1851,7 +1886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>422122</v>
       </c>
@@ -1859,7 +1894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>422123</v>
       </c>
@@ -1870,7 +1905,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>422124</v>
       </c>
@@ -1881,7 +1916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>422125</v>
       </c>
@@ -1892,7 +1927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>422126</v>
       </c>
@@ -1900,7 +1935,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>422127</v>
       </c>
@@ -1908,7 +1943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>422128</v>
       </c>
@@ -1919,7 +1954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>422129</v>
       </c>
@@ -1927,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>422130</v>
       </c>
@@ -1935,7 +1970,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>422131</v>
       </c>
@@ -1946,12 +1981,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>422132</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>422133</v>
       </c>
@@ -1959,7 +1994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>422134</v>
       </c>
@@ -1970,7 +2005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>422135</v>
       </c>
@@ -1981,12 +2016,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>422136</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>422137</v>
       </c>
@@ -1997,7 +2032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>422138</v>
       </c>
@@ -2005,7 +2040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>422139</v>
       </c>
@@ -2016,7 +2051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>422140</v>
       </c>
@@ -2027,7 +2062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>422141</v>
       </c>
@@ -2035,7 +2070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>422142</v>
       </c>
@@ -2043,7 +2078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>422143</v>
       </c>
@@ -2054,7 +2089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>422144</v>
       </c>
@@ -2065,7 +2100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>422145</v>
       </c>
@@ -2073,7 +2108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>422146</v>
       </c>
@@ -2087,7 +2122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>422147</v>
       </c>
@@ -2101,7 +2136,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>422148</v>
       </c>

--- a/Graduation Project/Project Data/original/Manufacturing Downtime/Manufacturing_Line_Productivity.xlsx
+++ b/Graduation Project/Project Data/original/Manufacturing Downtime/Manufacturing_Line_Productivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ATG\Documents\GitHub\Project-DEPI\Graduation Project\Project Data\original\Manufacturing Downtime\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ATG\OneDrive\Documents\GitHub\Project-DEPI\Graduation Project\Project Data\original\Manufacturing Downtime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBE059B-5348-4118-97AB-454C071916F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C04C1FD-EFE8-4AD4-8C2E-21A0CF393D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FF62ED8-A67E-423F-8325-F23DB684777C}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{8FF62ED8-A67E-423F-8325-F23DB684777C}"/>
   </bookViews>
   <sheets>
     <sheet name="Line productivity" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Oliver</t>
-  </si>
-  <si>
-    <t>Reece</t>
   </si>
 </sst>
 </file>
@@ -632,19 +629,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D962F3-8C54-4C2B-8E48-722D67F8C002}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" customWidth="1"/>
-    <col min="4" max="5" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="8.81640625" customWidth="1"/>
-    <col min="13" max="13" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="4" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.85546875" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -664,7 +661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45533</v>
       </c>
@@ -685,7 +682,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45533</v>
       </c>
@@ -706,7 +703,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45533</v>
       </c>
@@ -727,7 +724,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45533</v>
       </c>
@@ -748,7 +745,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45533</v>
       </c>
@@ -769,7 +766,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45533</v>
       </c>
@@ -790,7 +787,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45533</v>
       </c>
@@ -811,7 +808,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45534</v>
       </c>
@@ -832,7 +829,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45534</v>
       </c>
@@ -852,7 +849,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45534</v>
       </c>
@@ -872,7 +869,7 @@
         <v>0.39027777777777778</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45534</v>
       </c>
@@ -892,7 +889,7 @@
         <v>0.44236111111111109</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45534</v>
       </c>
@@ -912,7 +909,7 @@
         <v>0.50138888888888888</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45534</v>
       </c>
@@ -932,7 +929,7 @@
         <v>0.59375</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45534</v>
       </c>
@@ -952,7 +949,7 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45534</v>
       </c>
@@ -972,7 +969,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45534</v>
       </c>
@@ -983,7 +980,7 @@
         <v>422126</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3">
         <v>0.71875</v>
@@ -992,7 +989,7 @@
         <v>0.79097222222222219</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45534</v>
       </c>
@@ -1003,7 +1000,7 @@
         <v>422127</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3">
         <v>0.79097222222222219</v>
@@ -1012,7 +1009,7 @@
         <v>0.84861111111111109</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45534</v>
       </c>
@@ -1023,7 +1020,7 @@
         <v>422128</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3">
         <v>0.84861111111111109</v>
@@ -1032,7 +1029,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45534</v>
       </c>
@@ -1043,7 +1040,7 @@
         <v>422129</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" s="3">
         <v>0.92638888888888893</v>
@@ -1052,7 +1049,7 @@
         <v>0.97847222222222219</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45535</v>
       </c>
@@ -1063,7 +1060,7 @@
         <v>422130</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3">
         <v>0.32291666666666669</v>
@@ -1072,7 +1069,7 @@
         <v>0.37847222222222221</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45535</v>
       </c>
@@ -1083,7 +1080,7 @@
         <v>422131</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="3">
         <v>0.37847222222222221</v>
@@ -1092,7 +1089,7 @@
         <v>0.44097222222222221</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45535</v>
       </c>
@@ -1103,7 +1100,7 @@
         <v>422132</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" s="3">
         <v>0.44097222222222221</v>
@@ -1112,7 +1109,7 @@
         <v>0.4826388888888889</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45535</v>
       </c>
@@ -1123,7 +1120,7 @@
         <v>422133</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3">
         <v>0.4826388888888889</v>
@@ -1132,7 +1129,7 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45535</v>
       </c>
@@ -1143,7 +1140,7 @@
         <v>422134</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="3">
         <v>0.53819444444444442</v>
@@ -1152,7 +1149,7 @@
         <v>0.61458333333333337</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45535</v>
       </c>
@@ -1163,7 +1160,7 @@
         <v>422135</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3">
         <v>0.61458333333333337</v>
@@ -1172,7 +1169,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45535</v>
       </c>
@@ -1183,7 +1180,7 @@
         <v>422136</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" s="3">
         <v>0.6875</v>
@@ -1192,7 +1189,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45537</v>
       </c>
@@ -1203,7 +1200,7 @@
         <v>422137</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E28" s="3">
         <v>4.1666666666666664E-2</v>
@@ -1212,7 +1209,7 @@
         <v>0.11458333333333333</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45537</v>
       </c>
@@ -1223,7 +1220,7 @@
         <v>422138</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E29" s="3">
         <v>0.11458333333333333</v>
@@ -1232,7 +1229,7 @@
         <v>0.1701388888888889</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45537</v>
       </c>
@@ -1243,7 +1240,7 @@
         <v>422139</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3">
         <v>0.1701388888888889</v>
@@ -1252,7 +1249,7 @@
         <v>0.2361111111111111</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45537</v>
       </c>
@@ -1263,7 +1260,7 @@
         <v>422140</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3">
         <v>0.2361111111111111</v>
@@ -1272,7 +1269,7 @@
         <v>0.3215277777777778</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45537</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>422141</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E32" s="3">
         <v>0.3215277777777778</v>
@@ -1292,7 +1289,7 @@
         <v>0.36805555555555558</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45537</v>
       </c>
@@ -1303,7 +1300,7 @@
         <v>422142</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E33" s="3">
         <v>0.36805555555555558</v>
@@ -1312,7 +1309,7 @@
         <v>0.43055555555555558</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45537</v>
       </c>
@@ -1323,7 +1320,7 @@
         <v>422143</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" s="3">
         <v>0.43055555555555558</v>
@@ -1332,7 +1329,7 @@
         <v>0.51249999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45537</v>
       </c>
@@ -1343,7 +1340,7 @@
         <v>422144</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="3">
         <v>0.51249999999999996</v>
@@ -1352,7 +1349,7 @@
         <v>0.61805555555555558</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45537</v>
       </c>
@@ -1363,7 +1360,7 @@
         <v>422145</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3">
         <v>0.61805555555555558</v>
@@ -1372,7 +1369,7 @@
         <v>0.70138888888888895</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45537</v>
       </c>
@@ -1383,7 +1380,7 @@
         <v>422146</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E37" s="3">
         <v>0.70138888888888895</v>
@@ -1392,7 +1389,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45537</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>422147</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E38" s="3">
         <v>0.8125</v>
@@ -1412,7 +1409,7 @@
         <v>0.95486111111111116</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45538</v>
       </c>
@@ -1423,7 +1420,7 @@
         <v>422148</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E39" s="3">
         <v>0.95486111111111116</v>
@@ -1440,13 +1437,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FA7A9A-369F-46C5-93C5-09FBB32FF7C0}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1460,7 +1457,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1474,7 +1471,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1488,7 +1485,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1502,7 +1499,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1516,7 +1513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1530,7 +1527,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1553,14 +1550,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB7156D-DBB5-4EA9-A733-8897AD1035D5}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1571,7 +1568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1582,7 +1579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1593,7 +1590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1604,7 +1601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1615,7 +1612,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1626,7 +1623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1637,7 +1634,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1648,7 +1645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1659,7 +1656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1670,7 +1667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1681,7 +1678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1692,7 +1689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1711,13 +1708,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E903E6B-C648-491E-9E5D-F67501FDD632}">
   <dimension ref="A1:M40"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" customWidth="1"/>
-    <col min="2" max="13" width="5.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
+    <col min="2" max="13" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>23</v>
       </c>
@@ -1733,7 +1730,7 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1774,7 +1771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>422111</v>
       </c>
@@ -1785,7 +1782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>422112</v>
       </c>
@@ -1796,7 +1793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>422113</v>
       </c>
@@ -1804,7 +1801,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>422114</v>
       </c>
@@ -1815,7 +1812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>422115</v>
       </c>
@@ -1823,12 +1820,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>422116</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>422117</v>
       </c>
@@ -1839,7 +1836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>422118</v>
       </c>
@@ -1856,7 +1853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>422119</v>
       </c>
@@ -1864,7 +1861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>422120</v>
       </c>
@@ -1878,7 +1875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>422121</v>
       </c>
@@ -1886,7 +1883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>422122</v>
       </c>
@@ -1894,7 +1891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>422123</v>
       </c>
@@ -1905,7 +1902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>422124</v>
       </c>
@@ -1916,7 +1913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>422125</v>
       </c>
@@ -1927,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>422126</v>
       </c>
@@ -1935,7 +1932,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>422127</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>422128</v>
       </c>
@@ -1954,7 +1951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>422129</v>
       </c>
@@ -1962,7 +1959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>422130</v>
       </c>
@@ -1970,7 +1967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>422131</v>
       </c>
@@ -1981,12 +1978,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>422132</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>422133</v>
       </c>
@@ -1994,7 +1991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>422134</v>
       </c>
@@ -2005,7 +2002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>422135</v>
       </c>
@@ -2016,12 +2013,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>422136</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>422137</v>
       </c>
@@ -2032,7 +2029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>422138</v>
       </c>
@@ -2040,7 +2037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>422139</v>
       </c>
@@ -2051,7 +2048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>422140</v>
       </c>
@@ -2062,7 +2059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>422141</v>
       </c>
@@ -2070,7 +2067,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>422142</v>
       </c>
@@ -2078,7 +2075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>422143</v>
       </c>
@@ -2089,7 +2086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>422144</v>
       </c>
@@ -2100,7 +2097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>422145</v>
       </c>
@@ -2108,7 +2105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>422146</v>
       </c>
@@ -2122,7 +2119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>422147</v>
       </c>
@@ -2136,7 +2133,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>422148</v>
       </c>
